--- a/be/excel-example/mau_xuat_tai_san.xlsx
+++ b/be/excel-example/mau_xuat_tai_san.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quan-ly-kho-quan-nhu\be\excel-example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tan\Downloads\quan-ly-kho-quan-nhu\be\excel-example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F32D9-33AA-45BE-A175-F4C2AB10764F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770995C5-AE61-4078-AC0F-8DA2250F2F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1044" yWindow="1188" windowWidth="14664" windowHeight="7224" xr2:uid="{8173CFB7-8A6E-4B9F-B64E-8C35635E3EF2}"/>
+    <workbookView xWindow="5184" yWindow="2136" windowWidth="13008" windowHeight="8964" xr2:uid="{8173CFB7-8A6E-4B9F-B64E-8C35635E3EF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,10 +47,10 @@
     <t>Tên tài sản</t>
   </si>
   <si>
-    <t>Súng trường CKC</t>
+    <t>Xe tải KamAZ 43118</t>
   </si>
   <si>
-    <t>BATCH-1-20251225-WBM6PA</t>
+    <t>BATCH-TEST-20260521-8O8DFO</t>
   </si>
 </sst>
 </file>
@@ -61,7 +61,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -90,7 +90,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -423,14 +423,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C9182D-42AF-437C-A161-DA04DA9A6B5E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" customWidth="1"/>
-    <col min="2" max="2" width="23.69921875" customWidth="1"/>
-    <col min="3" max="3" width="11.09765625" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,7 +441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
